--- a/SINGLE HADITH CONTENT/BOOK WISE FINAL UPDATED CONTENT/UR/UR_TIRMIDHI.xlsx
+++ b/SINGLE HADITH CONTENT/BOOK WISE FINAL UPDATED CONTENT/UR/UR_TIRMIDHI.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,56 +433,65 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>book_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>language_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>hadith_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>content</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>content_error_details</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>ur</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>3121</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>{"meta":{"title":"$book_name$ $hadith_number$ - پل صراط اور قیامت کا منظر | $publication$","description":"Read $book_name$ $hadith_number$ from the $chapter_name$ chapter. قیامت کے دن زمین بدلنے پر لوگ پل صراط پر ہوں گے۔"},"heading":{"title":"پل صراط کا حدیث: قیامت کے دن لوگ کہاں ہوں گے؟","description":"یہ حدیث قیامت کے ایک بڑے منظر کو صاف الفاظ میں بیان کرتی ہے۔ ام المؤمنین عائشہ رضی الله عنہا نے قرآن کی آیت پڑھی جس میں بتایا گیا ہے کہ اس دن زمین اور آسمان بدل دیے جائیں گے۔ انہوں نے رسول اللہ صلی اللہ علیہ وسلم سے پوچھا کہ اس وقت لوگ کہاں ہوں گے؟ آپ صلی اللہ علیہ وسلم نے جواب دیا کہ وہ پل صراط پر ہوں گے۔ اس حدیث کا اصل موضوع پل صراط، قیامت کا دن، اور آخرت کی حقیقت ہے۔ یہ ہمیں یاد دلاتی ہے کہ قیامت صرف ایک عام دن نہیں ہوگا، بلکہ زمین و آسمان کی حالت بدل جائے گی۔ اس وقت انسان اپنی دنیاوی طاقت، مال، یا مقام کے بجائے اللہ کے فیصلے کے سامنے ہوگا۔ حدیث کا پیغام مختصر ہے، مگر بہت گہرا ہے: آخرت کی تیاری کو سنجیدگی سے لینا چاہیے۔"},"teachings":["قیامت کے دن زمین اور آسمان کی حالت بدل دی جائے گی۔","رسول اللہ صلی اللہ علیہ وسلم نے بتایا کہ اس وقت لوگ پل صراط پر ہوں گے۔","آخرت کے سوالات صحابہ رضی اللہ عنہم سنجیدگی سے پوچھتے تھے۔","یہ حدیث قیامت اور پل صراط پر ایمان کو یاد دلاتی ہے۔"],"related_hadiths":[{"id":"2791a","book_id":"2","label":"Sahih Muslim"},{"id":"7439","book_id":"1","label":"Sahih Bukhari"},{"id":"183a","book_id":"2","label":"Sahih Muslim"}]}</t>
         </is>
       </c>
+      <c r="E2" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SINGLE HADITH CONTENT/BOOK WISE FINAL UPDATED CONTENT/UR/UR_TIRMIDHI.xlsx
+++ b/SINGLE HADITH CONTENT/BOOK WISE FINAL UPDATED CONTENT/UR/UR_TIRMIDHI.xlsx
@@ -60,8 +60,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -488,7 +492,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>{"meta":{"title":"$book_name$ $hadith_number$ - پل صراط اور قیامت کا منظر | $publication$","description":"Read $book_name$ $hadith_number$ from the $chapter_name$ chapter. قیامت کے دن زمین بدلنے پر لوگ پل صراط پر ہوں گے۔"},"heading":{"title":"پل صراط کا حدیث: قیامت کے دن لوگ کہاں ہوں گے؟","description":"یہ حدیث قیامت کے ایک بڑے منظر کو صاف الفاظ میں بیان کرتی ہے۔ ام المؤمنین عائشہ رضی الله عنہا نے قرآن کی آیت پڑھی جس میں بتایا گیا ہے کہ اس دن زمین اور آسمان بدل دیے جائیں گے۔ انہوں نے رسول اللہ صلی اللہ علیہ وسلم سے پوچھا کہ اس وقت لوگ کہاں ہوں گے؟ آپ صلی اللہ علیہ وسلم نے جواب دیا کہ وہ پل صراط پر ہوں گے۔ اس حدیث کا اصل موضوع پل صراط، قیامت کا دن، اور آخرت کی حقیقت ہے۔ یہ ہمیں یاد دلاتی ہے کہ قیامت صرف ایک عام دن نہیں ہوگا، بلکہ زمین و آسمان کی حالت بدل جائے گی۔ اس وقت انسان اپنی دنیاوی طاقت، مال، یا مقام کے بجائے اللہ کے فیصلے کے سامنے ہوگا۔ حدیث کا پیغام مختصر ہے، مگر بہت گہرا ہے: آخرت کی تیاری کو سنجیدگی سے لینا چاہیے۔"},"teachings":["قیامت کے دن زمین اور آسمان کی حالت بدل دی جائے گی۔","رسول اللہ صلی اللہ علیہ وسلم نے بتایا کہ اس وقت لوگ پل صراط پر ہوں گے۔","آخرت کے سوالات صحابہ رضی اللہ عنہم سنجیدگی سے پوچھتے تھے۔","یہ حدیث قیامت اور پل صراط پر ایمان کو یاد دلاتی ہے۔"],"related_hadiths":[{"id":"2791a","book_id":"2","label":"Sahih Muslim"},{"id":"7439","book_id":"1","label":"Sahih Bukhari"},{"id":"183a","book_id":"2","label":"Sahih Muslim"}]}</t>
+          <t>{"meta":{"title":"$book_name$ $hadith_number$ - پل صراط اور قیامت کا منظر | $publication$","description":"Read $book_name$ $hadith_number$ from the $chapter_name$ chapter. قیامت کے دن زمین بدلنے پر لوگ پل صراط پر ہوں گے۔"},"heading":{"title":"پل صراط کا حدیث: قیامت کے دن لوگ کہاں ہوں گے؟","description":"یہ حدیث قیامت کے ایک بڑے منظر کو صاف الفاظ میں بیان کرتی ہے۔ ام المؤمنین عائشہ رضی الله عنہا نے قرآن کی آیت پڑھی جس میں بتایا گیا ہے کہ اس دن زمین اور آسمان بدل دیے جائیں گے۔ انہوں نے رسول اللہ صلی اللہ علیہ وسلم سے پوچھا کہ اس وقت لوگ کہاں ہوں گے؟ آپ صلی اللہ علیہ وسلم نے جواب دیا کہ وہ پل صراط پر ہوں گے۔ اس حدیث کا اصل موضوع پل صراط، قیامت کا دن، اور آخرت کی حقیقت ہے۔ یہ ہمیں یاد دلاتی ہے کہ قیامت صرف ایک عام دن نہیں ہوگا، بلکہ زمین و آسمان کی حالت بدل جائے گی۔ اس وقت انسان اپنی دنیاوی طاقت، مال، یا مقام کے بجائے اللہ کے فیصلے کے سامنے ہوگا۔ حدیث کا پیغام مختصر ہے، مگر بہت گہرا ہے: آخرت کی تیاری کو سنجیدگی سے لینا چاہیے۔"},"teachings":["قیامت کے دن زمین اور آسمان کی حالت بدل دی جائے گی۔","رسول اللہ صلی اللہ علیہ وسلم نے بتایا کہ اس وقت لوگ پل صراط پر ہوں گے۔","آخرت کے سوالات صحابہ رضی اللہ عنہم سنجیدگی سے پوچھتے تھے۔","یہ حدیث قیامت اور پل صراط پر ایمان کو یاد دلاتی ہے۔"],"related_hadiths":[{"id":"2791a","book_id":"2","slug":"muslim","label":"صحیح مسلم"},{"id":"7439","book_id":"1","slug":"bukhari","label":"صحیح بخاری"},{"id":"183a","book_id":"2","slug":"muslim","label":"صحیح مسلم"}]}</t>
         </is>
       </c>
       <c r="E2" s="4" t="n"/>
